--- a/eaas_python/template_files/DTR_template_organic.xlsx
+++ b/eaas_python/template_files/DTR_template_organic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Veronica\Downloads\ver\dict_folder\dict_eeas\eaas_python\template_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C858C2B8-5215-4292-9A8F-6E2F9C779866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577F875-26B5-4A7B-BFAC-D370C94A4CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -986,65 +986,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1077,6 +1056,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1090,22 +1074,38 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1322,6 +1322,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0129252-D852-4BE9-835C-8CCF464FDE57}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:T63"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1346,52 +1349,52 @@
       <c r="T2" s="51"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
-      <c r="L3" s="62" t="s">
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="95"/>
+      <c r="L3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="64"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="94"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="95"/>
     </row>
     <row r="4" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="67"/>
-      <c r="L4" s="65" t="s">
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
+      <c r="L4" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="67"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="98"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
@@ -1415,22 +1418,22 @@
     </row>
     <row r="6" spans="1:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="101"/>
       <c r="J6" s="49"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="101"/>
+      <c r="O6" s="101"/>
+      <c r="P6" s="101"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="101"/>
+      <c r="S6" s="101"/>
       <c r="T6" s="49"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -1459,10 +1462,10 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
       <c r="I8" s="6"/>
       <c r="J8" s="49"/>
       <c r="L8" s="4" t="s">
@@ -1470,34 +1473,34 @@
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="59"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="102"/>
+      <c r="Q8" s="102"/>
+      <c r="R8" s="102"/>
       <c r="S8" s="6"/>
       <c r="T8" s="49"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="70"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="71"/>
       <c r="I9" s="6"/>
       <c r="J9" s="49"/>
-      <c r="L9" s="68" t="s">
+      <c r="L9" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="70"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="71"/>
       <c r="S9" s="6"/>
       <c r="T9" s="49"/>
     </row>
@@ -1526,47 +1529,47 @@
       <c r="T10" s="49"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="73" t="s">
+      <c r="D11" s="87"/>
+      <c r="E11" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="74"/>
-      <c r="G11" s="73" t="s">
+      <c r="F11" s="87"/>
+      <c r="G11" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="75"/>
-      <c r="I11" s="95" t="s">
+      <c r="H11" s="88"/>
+      <c r="I11" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="L11" s="71" t="s">
+      <c r="J11" s="90"/>
+      <c r="L11" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="M11" s="73" t="s">
+      <c r="M11" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="74"/>
-      <c r="O11" s="73" t="s">
+      <c r="N11" s="87"/>
+      <c r="O11" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="73" t="s">
+      <c r="P11" s="87"/>
+      <c r="Q11" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="75"/>
-      <c r="S11" s="95" t="s">
+      <c r="R11" s="88"/>
+      <c r="S11" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="T11" s="96"/>
+      <c r="T11" s="90"/>
     </row>
     <row r="12" spans="1:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="72"/>
+      <c r="B12" s="100"/>
       <c r="C12" s="7" t="s">
         <v>9</v>
       </c>
@@ -1585,9 +1588,9 @@
       <c r="H12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="97"/>
-      <c r="J12" s="98"/>
-      <c r="L12" s="72"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
+      <c r="L12" s="100"/>
       <c r="M12" s="7" t="s">
         <v>9</v>
       </c>
@@ -1606,8 +1609,8 @@
       <c r="R12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="S12" s="97"/>
-      <c r="T12" s="98"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="92"/>
     </row>
     <row r="13" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38"/>
@@ -1618,8 +1621,8 @@
       <c r="F13" s="54"/>
       <c r="G13" s="55"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="79"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="69"/>
       <c r="K13" s="38"/>
       <c r="L13" s="27"/>
       <c r="M13" s="54"/>
@@ -1628,8 +1631,8 @@
       <c r="P13" s="54"/>
       <c r="Q13" s="55"/>
       <c r="R13" s="56"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="79"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="69"/>
     </row>
     <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="38"/>
@@ -1642,8 +1645,8 @@
       <c r="F14" s="8"/>
       <c r="G14" s="29"/>
       <c r="H14" s="39"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="79"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="69"/>
       <c r="K14" s="38"/>
       <c r="L14" s="28">
         <v>1</v>
@@ -1654,8 +1657,8 @@
       <c r="P14" s="8"/>
       <c r="Q14" s="29"/>
       <c r="R14" s="39"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="79"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="69"/>
     </row>
     <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="38"/>
@@ -1668,8 +1671,8 @@
       <c r="F15" s="17"/>
       <c r="G15" s="29"/>
       <c r="H15" s="39"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="79"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="69"/>
       <c r="K15" s="38"/>
       <c r="L15" s="31">
         <v>2</v>
@@ -1680,8 +1683,8 @@
       <c r="P15" s="17"/>
       <c r="Q15" s="29"/>
       <c r="R15" s="39"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="79"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="69"/>
     </row>
     <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="38"/>
@@ -1694,8 +1697,8 @@
       <c r="F16" s="32"/>
       <c r="G16" s="30"/>
       <c r="H16" s="39"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="79"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="69"/>
       <c r="K16" s="38"/>
       <c r="L16" s="31">
         <v>3</v>
@@ -1706,8 +1709,8 @@
       <c r="P16" s="32"/>
       <c r="Q16" s="30"/>
       <c r="R16" s="39"/>
-      <c r="S16" s="78"/>
-      <c r="T16" s="79"/>
+      <c r="S16" s="68"/>
+      <c r="T16" s="69"/>
     </row>
     <row r="17" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="38"/>
@@ -1720,8 +1723,8 @@
       <c r="F17" s="32"/>
       <c r="G17" s="33"/>
       <c r="H17" s="40"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="79"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="69"/>
       <c r="K17" s="38"/>
       <c r="L17" s="31">
         <v>4</v>
@@ -1732,8 +1735,8 @@
       <c r="P17" s="32"/>
       <c r="Q17" s="33"/>
       <c r="R17" s="40"/>
-      <c r="S17" s="78"/>
-      <c r="T17" s="79"/>
+      <c r="S17" s="68"/>
+      <c r="T17" s="69"/>
     </row>
     <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="38"/>
@@ -1746,8 +1749,8 @@
       <c r="F18" s="32"/>
       <c r="G18" s="33"/>
       <c r="H18" s="39"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="79"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="69"/>
       <c r="K18" s="38"/>
       <c r="L18" s="31">
         <v>5</v>
@@ -1758,8 +1761,8 @@
       <c r="P18" s="32"/>
       <c r="Q18" s="33"/>
       <c r="R18" s="39"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="79"/>
+      <c r="S18" s="68"/>
+      <c r="T18" s="69"/>
     </row>
     <row r="19" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="38"/>
@@ -1772,8 +1775,8 @@
       <c r="F19" s="20"/>
       <c r="G19" s="34"/>
       <c r="H19" s="41"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="79"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="69"/>
       <c r="K19" s="38"/>
       <c r="L19" s="31">
         <v>6</v>
@@ -1784,8 +1787,8 @@
       <c r="P19" s="20"/>
       <c r="Q19" s="34"/>
       <c r="R19" s="41"/>
-      <c r="S19" s="78"/>
-      <c r="T19" s="79"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="69"/>
     </row>
     <row r="20" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="38"/>
@@ -1798,8 +1801,8 @@
       <c r="F20" s="16"/>
       <c r="G20" s="30"/>
       <c r="H20" s="39"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="79"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="69"/>
       <c r="K20" s="38"/>
       <c r="L20" s="31">
         <v>7</v>
@@ -1810,8 +1813,8 @@
       <c r="P20" s="16"/>
       <c r="Q20" s="30"/>
       <c r="R20" s="39"/>
-      <c r="S20" s="78"/>
-      <c r="T20" s="79"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="69"/>
     </row>
     <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="38"/>
@@ -1824,8 +1827,8 @@
       <c r="F21" s="16"/>
       <c r="G21" s="30"/>
       <c r="H21" s="40"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="79"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="69"/>
       <c r="K21" s="38"/>
       <c r="L21" s="31">
         <v>8</v>
@@ -1836,8 +1839,8 @@
       <c r="P21" s="16"/>
       <c r="Q21" s="30"/>
       <c r="R21" s="40"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="79"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="69"/>
     </row>
     <row r="22" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="38"/>
@@ -1850,8 +1853,8 @@
       <c r="F22" s="23"/>
       <c r="G22" s="30"/>
       <c r="H22" s="39"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="79"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="69"/>
       <c r="K22" s="38"/>
       <c r="L22" s="31">
         <v>9</v>
@@ -1862,8 +1865,8 @@
       <c r="P22" s="23"/>
       <c r="Q22" s="30"/>
       <c r="R22" s="39"/>
-      <c r="S22" s="78"/>
-      <c r="T22" s="79"/>
+      <c r="S22" s="68"/>
+      <c r="T22" s="69"/>
     </row>
     <row r="23" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="38"/>
@@ -1876,8 +1879,8 @@
       <c r="F23" s="32"/>
       <c r="G23" s="33"/>
       <c r="H23" s="39"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="79"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="69"/>
       <c r="K23" s="38"/>
       <c r="L23" s="31">
         <v>10</v>
@@ -1888,8 +1891,8 @@
       <c r="P23" s="32"/>
       <c r="Q23" s="33"/>
       <c r="R23" s="39"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="79"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="69"/>
     </row>
     <row r="24" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="38"/>
@@ -1902,8 +1905,8 @@
       <c r="F24" s="32"/>
       <c r="G24" s="33"/>
       <c r="H24" s="39"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="79"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="69"/>
       <c r="K24" s="38"/>
       <c r="L24" s="31">
         <v>11</v>
@@ -1914,8 +1917,8 @@
       <c r="P24" s="32"/>
       <c r="Q24" s="33"/>
       <c r="R24" s="39"/>
-      <c r="S24" s="78"/>
-      <c r="T24" s="79"/>
+      <c r="S24" s="68"/>
+      <c r="T24" s="69"/>
     </row>
     <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="38"/>
@@ -1928,8 +1931,8 @@
       <c r="F25" s="32"/>
       <c r="G25" s="35"/>
       <c r="H25" s="42"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="79"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="69"/>
       <c r="K25" s="38"/>
       <c r="L25" s="31">
         <v>12</v>
@@ -1940,8 +1943,8 @@
       <c r="P25" s="32"/>
       <c r="Q25" s="35"/>
       <c r="R25" s="42"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="79"/>
+      <c r="S25" s="68"/>
+      <c r="T25" s="69"/>
     </row>
     <row r="26" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="38"/>
@@ -1954,8 +1957,8 @@
       <c r="F26" s="25"/>
       <c r="G26" s="36"/>
       <c r="H26" s="43"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="79"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="69"/>
       <c r="K26" s="38"/>
       <c r="L26" s="31">
         <v>13</v>
@@ -1966,8 +1969,8 @@
       <c r="P26" s="25"/>
       <c r="Q26" s="36"/>
       <c r="R26" s="43"/>
-      <c r="S26" s="78"/>
-      <c r="T26" s="79"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="69"/>
     </row>
     <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="38"/>
@@ -1980,8 +1983,8 @@
       <c r="F27" s="25"/>
       <c r="G27" s="36"/>
       <c r="H27" s="43"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="79"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="69"/>
       <c r="K27" s="38"/>
       <c r="L27" s="31">
         <v>14</v>
@@ -1992,8 +1995,8 @@
       <c r="P27" s="25"/>
       <c r="Q27" s="36"/>
       <c r="R27" s="43"/>
-      <c r="S27" s="78"/>
-      <c r="T27" s="79"/>
+      <c r="S27" s="68"/>
+      <c r="T27" s="69"/>
     </row>
     <row r="28" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="38"/>
@@ -2006,8 +2009,8 @@
       <c r="F28" s="25"/>
       <c r="G28" s="35"/>
       <c r="H28" s="44"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="79"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="69"/>
       <c r="K28" s="38"/>
       <c r="L28" s="31">
         <v>15</v>
@@ -2018,8 +2021,8 @@
       <c r="P28" s="25"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="44"/>
-      <c r="S28" s="78"/>
-      <c r="T28" s="79"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="69"/>
     </row>
     <row r="29" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="38"/>
@@ -2032,8 +2035,8 @@
       <c r="F29" s="25"/>
       <c r="G29" s="34"/>
       <c r="H29" s="45"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="79"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="69"/>
       <c r="K29" s="38"/>
       <c r="L29" s="31">
         <v>16</v>
@@ -2044,8 +2047,8 @@
       <c r="P29" s="25"/>
       <c r="Q29" s="34"/>
       <c r="R29" s="45"/>
-      <c r="S29" s="78"/>
-      <c r="T29" s="79"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="69"/>
     </row>
     <row r="30" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="38"/>
@@ -2058,8 +2061,8 @@
       <c r="F30" s="25"/>
       <c r="G30" s="33"/>
       <c r="H30" s="46"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="79"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="69"/>
       <c r="K30" s="38"/>
       <c r="L30" s="31">
         <v>17</v>
@@ -2070,8 +2073,8 @@
       <c r="P30" s="25"/>
       <c r="Q30" s="33"/>
       <c r="R30" s="46"/>
-      <c r="S30" s="78"/>
-      <c r="T30" s="79"/>
+      <c r="S30" s="68"/>
+      <c r="T30" s="69"/>
     </row>
     <row r="31" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="38"/>
@@ -2084,8 +2087,8 @@
       <c r="F31" s="32"/>
       <c r="G31" s="30"/>
       <c r="H31" s="46"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="79"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="69"/>
       <c r="K31" s="38"/>
       <c r="L31" s="31">
         <v>18</v>
@@ -2096,8 +2099,8 @@
       <c r="P31" s="32"/>
       <c r="Q31" s="30"/>
       <c r="R31" s="46"/>
-      <c r="S31" s="78"/>
-      <c r="T31" s="79"/>
+      <c r="S31" s="68"/>
+      <c r="T31" s="69"/>
     </row>
     <row r="32" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="38"/>
@@ -2110,8 +2113,8 @@
       <c r="F32" s="32"/>
       <c r="G32" s="34"/>
       <c r="H32" s="47"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="79"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="69"/>
       <c r="K32" s="38"/>
       <c r="L32" s="31">
         <v>19</v>
@@ -2122,8 +2125,8 @@
       <c r="P32" s="32"/>
       <c r="Q32" s="34"/>
       <c r="R32" s="47"/>
-      <c r="S32" s="78"/>
-      <c r="T32" s="79"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="69"/>
     </row>
     <row r="33" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="38"/>
@@ -2136,8 +2139,8 @@
       <c r="F33" s="25"/>
       <c r="G33" s="30"/>
       <c r="H33" s="46"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="79"/>
+      <c r="I33" s="68"/>
+      <c r="J33" s="69"/>
       <c r="K33" s="38"/>
       <c r="L33" s="31">
         <v>20</v>
@@ -2148,8 +2151,8 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="30"/>
       <c r="R33" s="46"/>
-      <c r="S33" s="78"/>
-      <c r="T33" s="79"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="69"/>
     </row>
     <row r="34" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="38"/>
@@ -2162,8 +2165,8 @@
       <c r="F34" s="25"/>
       <c r="G34" s="34"/>
       <c r="H34" s="46"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="79"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="69"/>
       <c r="K34" s="38"/>
       <c r="L34" s="31">
         <v>21</v>
@@ -2174,8 +2177,8 @@
       <c r="P34" s="25"/>
       <c r="Q34" s="34"/>
       <c r="R34" s="46"/>
-      <c r="S34" s="78"/>
-      <c r="T34" s="79"/>
+      <c r="S34" s="68"/>
+      <c r="T34" s="69"/>
     </row>
     <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="38"/>
@@ -2188,8 +2191,8 @@
       <c r="F35" s="25"/>
       <c r="G35" s="34"/>
       <c r="H35" s="48"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="79"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="69"/>
       <c r="K35" s="38"/>
       <c r="L35" s="31">
         <v>22</v>
@@ -2200,8 +2203,8 @@
       <c r="P35" s="25"/>
       <c r="Q35" s="34"/>
       <c r="R35" s="48"/>
-      <c r="S35" s="78"/>
-      <c r="T35" s="79"/>
+      <c r="S35" s="68"/>
+      <c r="T35" s="69"/>
     </row>
     <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="38"/>
@@ -2214,8 +2217,8 @@
       <c r="F36" s="25"/>
       <c r="G36" s="34"/>
       <c r="H36" s="48"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="79"/>
+      <c r="I36" s="68"/>
+      <c r="J36" s="69"/>
       <c r="K36" s="38"/>
       <c r="L36" s="31">
         <v>23</v>
@@ -2226,8 +2229,8 @@
       <c r="P36" s="25"/>
       <c r="Q36" s="34"/>
       <c r="R36" s="48"/>
-      <c r="S36" s="78"/>
-      <c r="T36" s="79"/>
+      <c r="S36" s="68"/>
+      <c r="T36" s="69"/>
     </row>
     <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="38"/>
@@ -2240,8 +2243,8 @@
       <c r="F37" s="25"/>
       <c r="G37" s="34"/>
       <c r="H37" s="48"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="79"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="69"/>
       <c r="K37" s="38"/>
       <c r="L37" s="31">
         <v>24</v>
@@ -2252,8 +2255,8 @@
       <c r="P37" s="25"/>
       <c r="Q37" s="34"/>
       <c r="R37" s="48"/>
-      <c r="S37" s="78"/>
-      <c r="T37" s="79"/>
+      <c r="S37" s="68"/>
+      <c r="T37" s="69"/>
     </row>
     <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="38"/>
@@ -2266,8 +2269,8 @@
       <c r="F38" s="32"/>
       <c r="G38" s="33"/>
       <c r="H38" s="48"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="79"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="69"/>
       <c r="K38" s="38"/>
       <c r="L38" s="31">
         <v>25</v>
@@ -2278,8 +2281,8 @@
       <c r="P38" s="32"/>
       <c r="Q38" s="33"/>
       <c r="R38" s="48"/>
-      <c r="S38" s="78"/>
-      <c r="T38" s="79"/>
+      <c r="S38" s="68"/>
+      <c r="T38" s="69"/>
     </row>
     <row r="39" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="38"/>
@@ -2292,8 +2295,8 @@
       <c r="F39" s="32"/>
       <c r="G39" s="34"/>
       <c r="H39" s="48"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="79"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="69"/>
       <c r="K39" s="38"/>
       <c r="L39" s="31">
         <v>26</v>
@@ -2304,8 +2307,8 @@
       <c r="P39" s="32"/>
       <c r="Q39" s="34"/>
       <c r="R39" s="48"/>
-      <c r="S39" s="78"/>
-      <c r="T39" s="79"/>
+      <c r="S39" s="68"/>
+      <c r="T39" s="69"/>
     </row>
     <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="38"/>
@@ -2318,8 +2321,8 @@
       <c r="F40" s="32"/>
       <c r="G40" s="34"/>
       <c r="H40" s="48"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="79"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="69"/>
       <c r="K40" s="38"/>
       <c r="L40" s="31">
         <v>27</v>
@@ -2330,8 +2333,8 @@
       <c r="P40" s="32"/>
       <c r="Q40" s="34"/>
       <c r="R40" s="48"/>
-      <c r="S40" s="78"/>
-      <c r="T40" s="79"/>
+      <c r="S40" s="68"/>
+      <c r="T40" s="69"/>
     </row>
     <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="38"/>
@@ -2344,8 +2347,8 @@
       <c r="F41" s="32"/>
       <c r="G41" s="34"/>
       <c r="H41" s="48"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="79"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="69"/>
       <c r="K41" s="38"/>
       <c r="L41" s="31">
         <v>28</v>
@@ -2356,8 +2359,8 @@
       <c r="P41" s="32"/>
       <c r="Q41" s="34"/>
       <c r="R41" s="48"/>
-      <c r="S41" s="78"/>
-      <c r="T41" s="79"/>
+      <c r="S41" s="68"/>
+      <c r="T41" s="69"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="38"/>
@@ -2370,8 +2373,8 @@
       <c r="F42" s="32"/>
       <c r="G42" s="34"/>
       <c r="H42" s="48"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="79"/>
+      <c r="I42" s="68"/>
+      <c r="J42" s="69"/>
       <c r="K42" s="38"/>
       <c r="L42" s="31">
         <v>29</v>
@@ -2382,8 +2385,8 @@
       <c r="P42" s="32"/>
       <c r="Q42" s="34"/>
       <c r="R42" s="48"/>
-      <c r="S42" s="78"/>
-      <c r="T42" s="79"/>
+      <c r="S42" s="68"/>
+      <c r="T42" s="69"/>
     </row>
     <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="38"/>
@@ -2396,8 +2399,8 @@
       <c r="F43" s="32"/>
       <c r="G43" s="34"/>
       <c r="H43" s="48"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="79"/>
+      <c r="I43" s="68"/>
+      <c r="J43" s="69"/>
       <c r="K43" s="38"/>
       <c r="L43" s="31">
         <v>30</v>
@@ -2408,8 +2411,8 @@
       <c r="P43" s="32"/>
       <c r="Q43" s="34"/>
       <c r="R43" s="48"/>
-      <c r="S43" s="78"/>
-      <c r="T43" s="79"/>
+      <c r="S43" s="68"/>
+      <c r="T43" s="69"/>
     </row>
     <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="38"/>
@@ -2422,8 +2425,8 @@
       <c r="F44" s="32"/>
       <c r="G44" s="34"/>
       <c r="H44" s="48"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="79"/>
+      <c r="I44" s="68"/>
+      <c r="J44" s="69"/>
       <c r="K44" s="38"/>
       <c r="L44" s="31">
         <v>31</v>
@@ -2434,194 +2437,194 @@
       <c r="P44" s="32"/>
       <c r="Q44" s="34"/>
       <c r="R44" s="48"/>
-      <c r="S44" s="78"/>
-      <c r="T44" s="79"/>
+      <c r="S44" s="68"/>
+      <c r="T44" s="69"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B45" s="80"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="81"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="72"/>
       <c r="F45" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="86"/>
-      <c r="H45" s="87"/>
-      <c r="I45" s="87"/>
-      <c r="J45" s="88"/>
-      <c r="L45" s="80"/>
-      <c r="M45" s="70"/>
-      <c r="N45" s="70"/>
-      <c r="O45" s="81"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="78"/>
+      <c r="J45" s="79"/>
+      <c r="L45" s="70"/>
+      <c r="M45" s="71"/>
+      <c r="N45" s="71"/>
+      <c r="O45" s="72"/>
       <c r="P45" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="Q45" s="86"/>
-      <c r="R45" s="87"/>
-      <c r="S45" s="87"/>
-      <c r="T45" s="88"/>
+      <c r="Q45" s="77"/>
+      <c r="R45" s="78"/>
+      <c r="S45" s="78"/>
+      <c r="T45" s="79"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B46" s="82"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="81"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="72"/>
       <c r="F46" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G46" s="89"/>
-      <c r="H46" s="90"/>
-      <c r="I46" s="90"/>
-      <c r="J46" s="91"/>
-      <c r="L46" s="82"/>
-      <c r="M46" s="69"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="81"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="82"/>
+      <c r="L46" s="73"/>
+      <c r="M46" s="64"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="72"/>
       <c r="P46" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="Q46" s="89"/>
-      <c r="R46" s="90"/>
-      <c r="S46" s="90"/>
-      <c r="T46" s="91"/>
+      <c r="Q46" s="80"/>
+      <c r="R46" s="81"/>
+      <c r="S46" s="81"/>
+      <c r="T46" s="82"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B47" s="82"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="81"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="72"/>
       <c r="F47" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G47" s="89"/>
-      <c r="H47" s="90"/>
-      <c r="I47" s="90"/>
-      <c r="J47" s="91"/>
-      <c r="L47" s="82"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="81"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="82"/>
+      <c r="L47" s="73"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="72"/>
       <c r="P47" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q47" s="89"/>
-      <c r="R47" s="90"/>
-      <c r="S47" s="90"/>
-      <c r="T47" s="91"/>
+      <c r="Q47" s="80"/>
+      <c r="R47" s="81"/>
+      <c r="S47" s="81"/>
+      <c r="T47" s="82"/>
     </row>
     <row r="48" spans="1:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="83"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="85"/>
+      <c r="B48" s="74"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="76"/>
       <c r="F48" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="92"/>
-      <c r="H48" s="93"/>
-      <c r="I48" s="93"/>
-      <c r="J48" s="94"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="84"/>
-      <c r="N48" s="84"/>
-      <c r="O48" s="85"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="85"/>
+      <c r="L48" s="74"/>
+      <c r="M48" s="75"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="76"/>
       <c r="P48" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="Q48" s="92"/>
-      <c r="R48" s="93"/>
-      <c r="S48" s="93"/>
-      <c r="T48" s="94"/>
+      <c r="Q48" s="83"/>
+      <c r="R48" s="84"/>
+      <c r="S48" s="84"/>
+      <c r="T48" s="85"/>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="53"/>
-      <c r="C49" s="76" t="s">
+      <c r="C49" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="76"/>
-      <c r="I49" s="76"/>
-      <c r="J49" s="77"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="60"/>
       <c r="L49" s="53"/>
-      <c r="M49" s="76" t="s">
+      <c r="M49" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="N49" s="76"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="76"/>
-      <c r="Q49" s="76"/>
-      <c r="R49" s="76"/>
-      <c r="S49" s="76"/>
-      <c r="T49" s="77"/>
+      <c r="N49" s="59"/>
+      <c r="O49" s="59"/>
+      <c r="P49" s="59"/>
+      <c r="Q49" s="59"/>
+      <c r="R49" s="59"/>
+      <c r="S49" s="59"/>
+      <c r="T49" s="60"/>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="102"/>
-      <c r="D50" s="102"/>
-      <c r="E50" s="102"/>
-      <c r="F50" s="102"/>
-      <c r="G50" s="102"/>
-      <c r="H50" s="102"/>
-      <c r="I50" s="102"/>
-      <c r="J50" s="103"/>
-      <c r="L50" s="68" t="s">
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="J50" s="63"/>
+      <c r="L50" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="M50" s="102"/>
-      <c r="N50" s="102"/>
-      <c r="O50" s="102"/>
-      <c r="P50" s="102"/>
-      <c r="Q50" s="102"/>
-      <c r="R50" s="102"/>
-      <c r="S50" s="102"/>
-      <c r="T50" s="103"/>
+      <c r="M50" s="62"/>
+      <c r="N50" s="62"/>
+      <c r="O50" s="62"/>
+      <c r="P50" s="62"/>
+      <c r="Q50" s="62"/>
+      <c r="R50" s="62"/>
+      <c r="S50" s="62"/>
+      <c r="T50" s="63"/>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B51" s="68" t="s">
+      <c r="B51" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="102"/>
-      <c r="D51" s="102"/>
-      <c r="E51" s="102"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="102"/>
-      <c r="H51" s="102"/>
-      <c r="I51" s="102"/>
-      <c r="J51" s="103"/>
-      <c r="L51" s="68" t="s">
+      <c r="C51" s="62"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
+      <c r="F51" s="62"/>
+      <c r="G51" s="62"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="62"/>
+      <c r="J51" s="63"/>
+      <c r="L51" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="M51" s="102"/>
-      <c r="N51" s="102"/>
-      <c r="O51" s="102"/>
-      <c r="P51" s="102"/>
-      <c r="Q51" s="102"/>
-      <c r="R51" s="102"/>
-      <c r="S51" s="102"/>
-      <c r="T51" s="103"/>
+      <c r="M51" s="62"/>
+      <c r="N51" s="62"/>
+      <c r="O51" s="62"/>
+      <c r="P51" s="62"/>
+      <c r="Q51" s="62"/>
+      <c r="R51" s="62"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="63"/>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B52" s="68" t="s">
+      <c r="B52" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="64"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="6"/>
       <c r="J52" s="49"/>
-      <c r="L52" s="68" t="s">
+      <c r="L52" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="M52" s="69"/>
-      <c r="N52" s="69"/>
+      <c r="M52" s="64"/>
+      <c r="N52" s="64"/>
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
@@ -2671,47 +2674,47 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B55" s="11"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="60"/>
-      <c r="H55" s="60"/>
-      <c r="I55" s="60"/>
+      <c r="C55" s="103"/>
+      <c r="D55" s="103"/>
+      <c r="E55" s="103"/>
+      <c r="F55" s="103"/>
+      <c r="G55" s="103"/>
+      <c r="H55" s="103"/>
+      <c r="I55" s="103"/>
       <c r="J55" s="49"/>
       <c r="L55" s="11"/>
-      <c r="M55" s="60"/>
-      <c r="N55" s="60"/>
-      <c r="O55" s="60"/>
-      <c r="P55" s="60"/>
-      <c r="Q55" s="60"/>
-      <c r="R55" s="60"/>
-      <c r="S55" s="60"/>
+      <c r="M55" s="103"/>
+      <c r="N55" s="103"/>
+      <c r="O55" s="103"/>
+      <c r="P55" s="103"/>
+      <c r="Q55" s="103"/>
+      <c r="R55" s="103"/>
+      <c r="S55" s="103"/>
       <c r="T55" s="49"/>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B56" s="99" t="s">
+      <c r="B56" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="100"/>
-      <c r="D56" s="100"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="100"/>
-      <c r="G56" s="100"/>
-      <c r="H56" s="100"/>
-      <c r="I56" s="100"/>
-      <c r="J56" s="101"/>
-      <c r="L56" s="99" t="s">
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="67"/>
+      <c r="L56" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="M56" s="100"/>
-      <c r="N56" s="100"/>
-      <c r="O56" s="100"/>
-      <c r="P56" s="100"/>
-      <c r="Q56" s="100"/>
-      <c r="R56" s="100"/>
-      <c r="S56" s="100"/>
-      <c r="T56" s="101"/>
+      <c r="M56" s="66"/>
+      <c r="N56" s="66"/>
+      <c r="O56" s="66"/>
+      <c r="P56" s="66"/>
+      <c r="Q56" s="66"/>
+      <c r="R56" s="66"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="67"/>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B57" s="10" t="s">
@@ -2799,42 +2802,42 @@
     </row>
     <row r="61" spans="2:20" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B61" s="12"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
+      <c r="C61" s="104"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
       <c r="J61" s="49"/>
       <c r="L61" s="12"/>
-      <c r="M61" s="61"/>
-      <c r="N61" s="61"/>
-      <c r="O61" s="61"/>
-      <c r="P61" s="61"/>
-      <c r="Q61" s="61"/>
-      <c r="R61" s="61"/>
-      <c r="S61" s="61"/>
+      <c r="M61" s="104"/>
+      <c r="N61" s="104"/>
+      <c r="O61" s="104"/>
+      <c r="P61" s="104"/>
+      <c r="Q61" s="104"/>
+      <c r="R61" s="104"/>
+      <c r="S61" s="104"/>
       <c r="T61" s="49"/>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" s="57"/>
-      <c r="C62" s="104"/>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
       <c r="J62" s="49"/>
       <c r="L62" s="4"/>
-      <c r="M62" s="104"/>
-      <c r="N62" s="104"/>
-      <c r="O62" s="104"/>
-      <c r="P62" s="104"/>
-      <c r="Q62" s="104"/>
-      <c r="R62" s="104"/>
-      <c r="S62" s="104"/>
+      <c r="M62" s="58"/>
+      <c r="N62" s="58"/>
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
       <c r="T62" s="49"/>
     </row>
     <row r="63" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -2859,6 +2862,93 @@
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="L3:T3"/>
+    <mergeCell ref="L4:T4"/>
+    <mergeCell ref="L9:R9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="M6:S6"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="S11:T12"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B50:J50"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B45:E48"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S27:T27"/>
     <mergeCell ref="C62:I62"/>
     <mergeCell ref="M62:S62"/>
     <mergeCell ref="M49:T49"/>
@@ -2876,100 +2966,14 @@
     <mergeCell ref="Q46:T46"/>
     <mergeCell ref="Q47:T47"/>
     <mergeCell ref="Q48:T48"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="S37:T37"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="S33:T33"/>
     <mergeCell ref="B56:J56"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B50:J50"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="S11:T12"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="I11:J12"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="L3:T3"/>
-    <mergeCell ref="L4:T4"/>
-    <mergeCell ref="L9:R9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="B45:E48"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="M6:S6"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="O8:R8"/>
     <mergeCell ref="M55:S55"/>
     <mergeCell ref="M61:S61"/>
     <mergeCell ref="C55:I55"/>
     <mergeCell ref="C61:I61"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C49:J49"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
     <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="56" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>